--- a/data/input-sheet.xlsx
+++ b/data/input-sheet.xlsx
@@ -12,8 +12,8 @@
     <sheet name="基本情報" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="不動産" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="有価証券" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="預貯金" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="保険" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="保険" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="預貯金" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="その他の借入" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="検算" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
@@ -286,7 +286,7 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Unknown Author</author>
@@ -1722,7 +1722,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">預貯金　（</t>
+      <t xml:space="preserve">保険　（</t>
     </r>
     <r>
       <rPr>
@@ -1760,8 +1760,128 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">つの口座）</t>
-    </r>
+      <t xml:space="preserve">つの契約）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">貯蓄性のある保険（終身・養老・個人年金など）を書きます。掛け捨ての医療保険などは書きません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">評価額には「解約返戻金」（今解約したら戻る額）を入れます。毎年届く「ご契約内容のお知らせ」か保険会社のマイページで分かります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 死亡保険金額は参考です。今使えるお金ではないので、資産の合計には足しません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保険名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保険会社</t>
+  </si>
+  <si>
+    <t xml:space="preserve">払込保険料 累計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">解約返戻金</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">死亡保険金額
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">参考・資産に含めず</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">評価日</t>
+  </si>
+  <si>
+    <t xml:space="preserve">円換算した解約返戻金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">円換算した払込保険料</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（例）変額終身保険</t>
+  </si>
+  <si>
+    <t xml:space="preserve">○○生命</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-31</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">解約返戻金は年</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回の通知の数字</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">合計（見本行は数えません）</t>
   </si>
   <si>
     <r>
@@ -1771,7 +1891,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">同じ銀行に複数口座があるときは、まとめて</t>
+      <t xml:space="preserve">※ 解約返戻金がまだ分からないときは、払込保険料累計と同じ額を入れ、「補足」に「解約返戻金 未確認（暫定）」と書いてください。含み損益は </t>
     </r>
     <r>
       <rPr>
@@ -1781,7 +1901,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">±0 </t>
     </r>
     <r>
       <rPr>
@@ -1790,53 +1910,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">行にしても、分けて書いても構いません。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">金融機関</t>
-  </si>
-  <si>
-    <t xml:space="preserve">残高</t>
-  </si>
-  <si>
-    <t xml:space="preserve">円換算した残高</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（例）</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">銀行</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">合計（見本行は数えません）</t>
+      <t xml:space="preserve">になります。</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1846,7 +1921,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">保険　（</t>
+      <t xml:space="preserve">預貯金　（</t>
     </r>
     <r>
       <rPr>
@@ -1884,124 +1959,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">つの契約）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">貯蓄性のある保険（終身・養老・個人年金など）を書きます。掛け捨ての医療保険などは書きません。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">評価額には「解約返戻金」（今解約したら戻る額）を入れます。毎年届く「ご契約内容のお知らせ」か保険会社のマイページで分かります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">※ 死亡保険金額は参考です。今使えるお金ではないので、資産の合計には足しません。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">保険名</t>
-  </si>
-  <si>
-    <t xml:space="preserve">保険会社</t>
-  </si>
-  <si>
-    <t xml:space="preserve">払込保険料 累計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">解約返戻金</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">死亡保険金額
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">参考・資産に含めず</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">評価日</t>
-  </si>
-  <si>
-    <t xml:space="preserve">円換算した解約返戻金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">円換算した払込保険料</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（例）変額終身保険</t>
-  </si>
-  <si>
-    <t xml:space="preserve">○○生命</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-31</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">解約返戻金は年</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回の通知の数字</t>
+      <t xml:space="preserve">つの口座）</t>
     </r>
   </si>
   <si>
@@ -2012,7 +1970,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">※ 解約返戻金がまだ分からないときは、払込保険料累計と同じ額を入れ、「補足」に「解約返戻金 未確認（暫定）」と書いてください。含み損益は </t>
+      <t xml:space="preserve">同じ銀行に複数口座があるときは、まとめて</t>
     </r>
     <r>
       <rPr>
@@ -2022,7 +1980,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">±0 </t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -2031,7 +1989,49 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">になります。</t>
+      <t xml:space="preserve">行にしても、分けて書いても構いません。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">金融機関</t>
+  </si>
+  <si>
+    <t xml:space="preserve">残高</t>
+  </si>
+  <si>
+    <t xml:space="preserve">円換算した残高</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（例）</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">銀行</t>
     </r>
   </si>
   <si>
@@ -4163,211 +4163,6 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="24" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D5" s="24" t="n">
-        <f aca="false">IF(A5="","",ROUND(C5*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B5,基本情報!$A$10:$A$13,0)),0),0))</f>
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="30"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="28" t="str">
-        <f aca="false">IF(A6="","",ROUND(C6*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B6,基本情報!$A$10:$A$13,0)),0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="30"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="28" t="str">
-        <f aca="false">IF(A7="","",ROUND(C7*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B7,基本情報!$A$10:$A$13,0)),0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="30"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="28" t="str">
-        <f aca="false">IF(A8="","",ROUND(C8*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B8,基本情報!$A$10:$A$13,0)),0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="30"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="28" t="str">
-        <f aca="false">IF(A9="","",ROUND(C9*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B9,基本情報!$A$10:$A$13,0)),0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="30"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="28" t="str">
-        <f aca="false">IF(A10="","",ROUND(C10*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B10,基本情報!$A$10:$A$13,0)),0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="28" t="str">
-        <f aca="false">IF(A11="","",ROUND(C11*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B11,基本情報!$A$10:$A$13,0)),0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="30"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="28" t="str">
-        <f aca="false">IF(A12="","",ROUND(C12*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B12,基本情報!$A$10:$A$13,0)),0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="30"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="28" t="str">
-        <f aca="false">IF(A13="","",ROUND(C13*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B13,基本情報!$A$10:$A$13,0)),0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="30"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="28" t="str">
-        <f aca="false">IF(A14="","",ROUND(C14*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B14,基本情報!$A$10:$A$13,0)),0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="30"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="28" t="str">
-        <f aca="false">IF(A15="","",ROUND(C15*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B15,基本情報!$A$10:$A$13,0)),0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="30"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="28" t="str">
-        <f aca="false">IF(A16="","",ROUND(C16*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B16,基本情報!$A$10:$A$13,0)),0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="30"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="28" t="str">
-        <f aca="false">IF(A17="","",ROUND(C17*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B17,基本情報!$A$10:$A$13,0)),0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="30"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="28" t="str">
-        <f aca="false">IF(A18="","",ROUND(C18*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B18,基本情報!$A$10:$A$13,0)),0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="30"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="28" t="str">
-        <f aca="false">IF(A19="","",ROUND(C19*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B19,基本情報!$A$10:$A$13,0)),0),0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="31" t="n">
-        <f aca="false">SUM(D6:D19)</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B5:B19" type="list">
-      <formula1>"JPY,USD,EUR"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="true"/>
-  </sheetPr>
   <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -4384,45 +4179,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>32</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="H6" s="21" t="s">
         <v>75</v>
@@ -4431,18 +4226,18 @@
         <v>76</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="K6" s="21" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>34</v>
@@ -4457,10 +4252,10 @@
         <v>10000000</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="I7" s="24" t="n">
         <f aca="false">IF(A7="","",E7-D7)</f>
@@ -4631,7 +4426,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="J15" s="31" t="n">
         <f aca="false">SUM(J8:J14)</f>
@@ -4644,7 +4439,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -4662,6 +4457,211 @@
     <oddFooter/>
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="24" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D5" s="24" t="n">
+        <f aca="false">IF(A5="","",ROUND(C5*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B5,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="30"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="28" t="str">
+        <f aca="false">IF(A6="","",ROUND(C6*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B6,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="30"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="28" t="str">
+        <f aca="false">IF(A7="","",ROUND(C7*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B7,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="30"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="28" t="str">
+        <f aca="false">IF(A8="","",ROUND(C8*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B8,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="30"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="28" t="str">
+        <f aca="false">IF(A9="","",ROUND(C9*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B9,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="30"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="28" t="str">
+        <f aca="false">IF(A10="","",ROUND(C10*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B10,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="30"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="28" t="str">
+        <f aca="false">IF(A11="","",ROUND(C11*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B11,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="30"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="28" t="str">
+        <f aca="false">IF(A12="","",ROUND(C12*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B12,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="30"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="28" t="str">
+        <f aca="false">IF(A13="","",ROUND(C13*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B13,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="30"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="28" t="str">
+        <f aca="false">IF(A14="","",ROUND(C14*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B14,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="30"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="28" t="str">
+        <f aca="false">IF(A15="","",ROUND(C15*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B15,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="30"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="28" t="str">
+        <f aca="false">IF(A16="","",ROUND(C16*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B16,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="30"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="28" t="str">
+        <f aca="false">IF(A17="","",ROUND(C17*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B17,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="30"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="28" t="str">
+        <f aca="false">IF(A18="","",ROUND(C18*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B18,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="30"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="28" t="str">
+        <f aca="false">IF(A19="","",ROUND(C19*IFERROR(INDEX(基本情報!$B$10:$B$13,MATCH(B19,基本情報!$A$10:$A$13,0)),0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="31" t="n">
+        <f aca="false">SUM(D6:D19)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B5:B19" type="list">
+      <formula1>"JPY,USD,EUR"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 

--- a/data/input-sheet.xlsx
+++ b/data/input-sheet.xlsx
@@ -260,6 +260,110 @@
         </r>
       </text>
     </comment>
+    <comment ref="R4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">今売ったらいくらか、の推定額です。空欄で構いません。全物件に入れると、①サマリーに総資産と純資産が出ます。</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">件でも空欄なら、純資産は出しません（実態より小さく出るため）。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">その時価をどう出したか。例</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">不動産会社の査定書 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">/ </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">取引事例 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">/ </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">路線価から換算 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">/ </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">自己推定。空欄で構いませんが、書いておくと後から根拠をたどれます。</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -321,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="185">
   <si>
     <t xml:space="preserve">資産ダッシュボード 入力シート</t>
   </si>
@@ -1380,6 +1484,141 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時価
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">任意</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">評価日
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">任意</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">評価の根拠
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">任意</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">総投資額</t>
   </si>
   <si>
@@ -1477,6 +1716,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">含み損益</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -1547,6 +1789,12 @@
       </rPr>
       <t xml:space="preserve">銀行</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不動産会社の査定書</t>
   </si>
   <si>
     <r>
@@ -1676,9 +1924,6 @@
     <t xml:space="preserve">補足（任意）</t>
   </si>
   <si>
-    <t xml:space="preserve">含み損益</t>
-  </si>
-  <si>
     <t xml:space="preserve">円換算した評価額</t>
   </si>
   <si>
@@ -2230,6 +2475,48 @@
     <t xml:space="preserve">家賃 − 返済 − 経費。マイナスなら持ち出しです</t>
   </si>
   <si>
+    <t xml:space="preserve">時価合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手で入れた推定値。空欄の物件は数えません</t>
+  </si>
+  <si>
+    <t xml:space="preserve">時価 − 総投資額（時価を入れた物件だけ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LTV</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">残債合計 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時価合計</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">負債</t>
   </si>
   <si>
@@ -2246,6 +2533,54 @@
   </si>
   <si>
     <t xml:space="preserve">不動産 ＋ その他</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総資産・純資産</t>
+  </si>
+  <si>
+    <t xml:space="preserve">時価を入れた物件数</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ここが揃うと下の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つが出ます</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">総資産</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金融資産 ＋ 不動産（時価）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">純資産</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総資産 − 総負債</t>
   </si>
   <si>
     <t xml:space="preserve">つじつまの確認</t>
@@ -2607,7 +2942,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2745,6 +3080,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3265,7 +3604,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -3280,12 +3619,15 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3365,19 +3707,31 @@
       <c r="V4" s="21" t="s">
         <v>62</v>
       </c>
+      <c r="W4" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="X4" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y4" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z4" s="21" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C5" s="22" t="n">
         <v>45.5</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>15</v>
@@ -3392,7 +3746,7 @@
         <v>35500000</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J5" s="25" t="n">
         <v>1.8</v>
@@ -3419,24 +3773,37 @@
         <v>108000</v>
       </c>
       <c r="R5" s="24" t="n">
+        <v>58000000</v>
+      </c>
+      <c r="S5" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="T5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="U5" s="24" t="n">
         <f aca="false">F5+G5</f>
         <v>50000000</v>
       </c>
-      <c r="S5" s="24" t="n">
+      <c r="V5" s="24" t="n">
         <f aca="false">G5-H5</f>
         <v>4500000</v>
       </c>
-      <c r="T5" s="24" t="n">
+      <c r="W5" s="24" t="n">
         <f aca="false">ROUND(Q5/12,0)</f>
         <v>9000</v>
       </c>
-      <c r="U5" s="24" t="n">
-        <f aca="false">N5-M5-O5-P5-T5</f>
+      <c r="X5" s="24" t="n">
+        <f aca="false">N5-M5-O5-P5-W5</f>
         <v>23000</v>
       </c>
-      <c r="V5" s="7" t="n">
+      <c r="Y5" s="7" t="n">
         <f aca="false">K5*12+L5</f>
         <v>323</v>
+      </c>
+      <c r="Z5" s="24" t="n">
+        <f aca="false">IF(R5="","",R5-U5)</f>
+        <v>8000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3457,25 +3824,32 @@
       <c r="O6" s="26"/>
       <c r="P6" s="26"/>
       <c r="Q6" s="26"/>
-      <c r="R6" s="28" t="n">
+      <c r="R6" s="26"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="28" t="n">
         <f aca="false">F6+G6</f>
         <v>0</v>
       </c>
-      <c r="S6" s="28" t="n">
+      <c r="V6" s="28" t="n">
         <f aca="false">G6-H6</f>
         <v>0</v>
       </c>
-      <c r="T6" s="28" t="n">
+      <c r="W6" s="28" t="n">
         <f aca="false">ROUND(Q6/12,0)</f>
         <v>0</v>
       </c>
-      <c r="U6" s="28" t="n">
-        <f aca="false">N6-M6-O6-P6-T6</f>
-        <v>0</v>
-      </c>
-      <c r="V6" s="17" t="n">
+      <c r="X6" s="28" t="n">
+        <f aca="false">N6-M6-O6-P6-W6</f>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="17" t="n">
         <f aca="false">K6*12+L6</f>
         <v>0</v>
+      </c>
+      <c r="Z6" s="28" t="str">
+        <f aca="false">IF(R6="","",R6-U6)</f>
+        <v/>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3496,25 +3870,32 @@
       <c r="O7" s="26"/>
       <c r="P7" s="26"/>
       <c r="Q7" s="26"/>
-      <c r="R7" s="28" t="n">
+      <c r="R7" s="26"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19"/>
+      <c r="U7" s="28" t="n">
         <f aca="false">F7+G7</f>
         <v>0</v>
       </c>
-      <c r="S7" s="28" t="n">
+      <c r="V7" s="28" t="n">
         <f aca="false">G7-H7</f>
         <v>0</v>
       </c>
-      <c r="T7" s="28" t="n">
+      <c r="W7" s="28" t="n">
         <f aca="false">ROUND(Q7/12,0)</f>
         <v>0</v>
       </c>
-      <c r="U7" s="28" t="n">
-        <f aca="false">N7-M7-O7-P7-T7</f>
-        <v>0</v>
-      </c>
-      <c r="V7" s="17" t="n">
+      <c r="X7" s="28" t="n">
+        <f aca="false">N7-M7-O7-P7-W7</f>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="17" t="n">
         <f aca="false">K7*12+L7</f>
         <v>0</v>
+      </c>
+      <c r="Z7" s="28" t="str">
+        <f aca="false">IF(R7="","",R7-U7)</f>
+        <v/>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3535,25 +3916,32 @@
       <c r="O8" s="26"/>
       <c r="P8" s="26"/>
       <c r="Q8" s="26"/>
-      <c r="R8" s="28" t="n">
+      <c r="R8" s="26"/>
+      <c r="S8" s="19"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="28" t="n">
         <f aca="false">F8+G8</f>
         <v>0</v>
       </c>
-      <c r="S8" s="28" t="n">
+      <c r="V8" s="28" t="n">
         <f aca="false">G8-H8</f>
         <v>0</v>
       </c>
-      <c r="T8" s="28" t="n">
+      <c r="W8" s="28" t="n">
         <f aca="false">ROUND(Q8/12,0)</f>
         <v>0</v>
       </c>
-      <c r="U8" s="28" t="n">
-        <f aca="false">N8-M8-O8-P8-T8</f>
-        <v>0</v>
-      </c>
-      <c r="V8" s="17" t="n">
+      <c r="X8" s="28" t="n">
+        <f aca="false">N8-M8-O8-P8-W8</f>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="17" t="n">
         <f aca="false">K8*12+L8</f>
         <v>0</v>
+      </c>
+      <c r="Z8" s="28" t="str">
+        <f aca="false">IF(R8="","",R8-U8)</f>
+        <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3574,25 +3962,32 @@
       <c r="O9" s="26"/>
       <c r="P9" s="26"/>
       <c r="Q9" s="26"/>
-      <c r="R9" s="28" t="n">
+      <c r="R9" s="26"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="28" t="n">
         <f aca="false">F9+G9</f>
         <v>0</v>
       </c>
-      <c r="S9" s="28" t="n">
+      <c r="V9" s="28" t="n">
         <f aca="false">G9-H9</f>
         <v>0</v>
       </c>
-      <c r="T9" s="28" t="n">
+      <c r="W9" s="28" t="n">
         <f aca="false">ROUND(Q9/12,0)</f>
         <v>0</v>
       </c>
-      <c r="U9" s="28" t="n">
-        <f aca="false">N9-M9-O9-P9-T9</f>
-        <v>0</v>
-      </c>
-      <c r="V9" s="17" t="n">
+      <c r="X9" s="28" t="n">
+        <f aca="false">N9-M9-O9-P9-W9</f>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="17" t="n">
         <f aca="false">K9*12+L9</f>
         <v>0</v>
+      </c>
+      <c r="Z9" s="28" t="str">
+        <f aca="false">IF(R9="","",R9-U9)</f>
+        <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3613,25 +4008,32 @@
       <c r="O10" s="26"/>
       <c r="P10" s="26"/>
       <c r="Q10" s="26"/>
-      <c r="R10" s="28" t="n">
+      <c r="R10" s="26"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="28" t="n">
         <f aca="false">F10+G10</f>
         <v>0</v>
       </c>
-      <c r="S10" s="28" t="n">
+      <c r="V10" s="28" t="n">
         <f aca="false">G10-H10</f>
         <v>0</v>
       </c>
-      <c r="T10" s="28" t="n">
+      <c r="W10" s="28" t="n">
         <f aca="false">ROUND(Q10/12,0)</f>
         <v>0</v>
       </c>
-      <c r="U10" s="28" t="n">
-        <f aca="false">N10-M10-O10-P10-T10</f>
-        <v>0</v>
-      </c>
-      <c r="V10" s="17" t="n">
+      <c r="X10" s="28" t="n">
+        <f aca="false">N10-M10-O10-P10-W10</f>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="17" t="n">
         <f aca="false">K10*12+L10</f>
         <v>0</v>
+      </c>
+      <c r="Z10" s="28" t="str">
+        <f aca="false">IF(R10="","",R10-U10)</f>
+        <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3652,25 +4054,32 @@
       <c r="O11" s="26"/>
       <c r="P11" s="26"/>
       <c r="Q11" s="26"/>
-      <c r="R11" s="28" t="n">
+      <c r="R11" s="26"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="28" t="n">
         <f aca="false">F11+G11</f>
         <v>0</v>
       </c>
-      <c r="S11" s="28" t="n">
+      <c r="V11" s="28" t="n">
         <f aca="false">G11-H11</f>
         <v>0</v>
       </c>
-      <c r="T11" s="28" t="n">
+      <c r="W11" s="28" t="n">
         <f aca="false">ROUND(Q11/12,0)</f>
         <v>0</v>
       </c>
-      <c r="U11" s="28" t="n">
-        <f aca="false">N11-M11-O11-P11-T11</f>
-        <v>0</v>
-      </c>
-      <c r="V11" s="17" t="n">
+      <c r="X11" s="28" t="n">
+        <f aca="false">N11-M11-O11-P11-W11</f>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="17" t="n">
         <f aca="false">K11*12+L11</f>
         <v>0</v>
+      </c>
+      <c r="Z11" s="28" t="str">
+        <f aca="false">IF(R11="","",R11-U11)</f>
+        <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3691,25 +4100,32 @@
       <c r="O12" s="26"/>
       <c r="P12" s="26"/>
       <c r="Q12" s="26"/>
-      <c r="R12" s="28" t="n">
+      <c r="R12" s="26"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="28" t="n">
         <f aca="false">F12+G12</f>
         <v>0</v>
       </c>
-      <c r="S12" s="28" t="n">
+      <c r="V12" s="28" t="n">
         <f aca="false">G12-H12</f>
         <v>0</v>
       </c>
-      <c r="T12" s="28" t="n">
+      <c r="W12" s="28" t="n">
         <f aca="false">ROUND(Q12/12,0)</f>
         <v>0</v>
       </c>
-      <c r="U12" s="28" t="n">
-        <f aca="false">N12-M12-O12-P12-T12</f>
-        <v>0</v>
-      </c>
-      <c r="V12" s="17" t="n">
+      <c r="X12" s="28" t="n">
+        <f aca="false">N12-M12-O12-P12-W12</f>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="17" t="n">
         <f aca="false">K12*12+L12</f>
         <v>0</v>
+      </c>
+      <c r="Z12" s="28" t="str">
+        <f aca="false">IF(R12="","",R12-U12)</f>
+        <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3730,25 +4146,32 @@
       <c r="O13" s="26"/>
       <c r="P13" s="26"/>
       <c r="Q13" s="26"/>
-      <c r="R13" s="28" t="n">
+      <c r="R13" s="26"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="28" t="n">
         <f aca="false">F13+G13</f>
         <v>0</v>
       </c>
-      <c r="S13" s="28" t="n">
+      <c r="V13" s="28" t="n">
         <f aca="false">G13-H13</f>
         <v>0</v>
       </c>
-      <c r="T13" s="28" t="n">
+      <c r="W13" s="28" t="n">
         <f aca="false">ROUND(Q13/12,0)</f>
         <v>0</v>
       </c>
-      <c r="U13" s="28" t="n">
-        <f aca="false">N13-M13-O13-P13-T13</f>
-        <v>0</v>
-      </c>
-      <c r="V13" s="17" t="n">
+      <c r="X13" s="28" t="n">
+        <f aca="false">N13-M13-O13-P13-W13</f>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="17" t="n">
         <f aca="false">K13*12+L13</f>
         <v>0</v>
+      </c>
+      <c r="Z13" s="28" t="str">
+        <f aca="false">IF(R13="","",R13-U13)</f>
+        <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3769,30 +4192,37 @@
       <c r="O14" s="26"/>
       <c r="P14" s="26"/>
       <c r="Q14" s="26"/>
-      <c r="R14" s="28" t="n">
+      <c r="R14" s="26"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="28" t="n">
         <f aca="false">F14+G14</f>
         <v>0</v>
       </c>
-      <c r="S14" s="28" t="n">
+      <c r="V14" s="28" t="n">
         <f aca="false">G14-H14</f>
         <v>0</v>
       </c>
-      <c r="T14" s="28" t="n">
+      <c r="W14" s="28" t="n">
         <f aca="false">ROUND(Q14/12,0)</f>
         <v>0</v>
       </c>
-      <c r="U14" s="28" t="n">
-        <f aca="false">N14-M14-O14-P14-T14</f>
-        <v>0</v>
-      </c>
-      <c r="V14" s="17" t="n">
+      <c r="X14" s="28" t="n">
+        <f aca="false">N14-M14-O14-P14-W14</f>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="17" t="n">
         <f aca="false">K14*12+L14</f>
         <v>0</v>
+      </c>
+      <c r="Z14" s="28" t="str">
+        <f aca="false">IF(R14="","",R14-U14)</f>
+        <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -3826,54 +4256,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>32</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="29" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>34</v>
@@ -3900,10 +4330,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="29" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>34</v>
@@ -3930,10 +4360,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="29" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>34</v>
@@ -3960,10 +4390,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="29" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>34</v>
@@ -3975,7 +4405,7 @@
         <v>1200000</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G9" s="28" t="n">
         <f aca="false">E9-D9</f>
@@ -3992,10 +4422,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="29" t="s">
         <v>85</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>80</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>36</v>
@@ -4022,10 +4452,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="29" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>36</v>
@@ -4052,10 +4482,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>36</v>
@@ -4082,10 +4512,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>36</v>
@@ -4097,7 +4527,7 @@
         <v>11000</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G13" s="28" t="n">
         <f aca="false">E13-D13</f>
@@ -4114,7 +4544,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D14" s="31" t="n">
         <f aca="false">SUM(D6:D13)</f>
@@ -4125,7 +4555,7 @@
         <v>10268500</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G14" s="31" t="n">
         <f aca="false">SUM(G6:G13)</f>
@@ -4179,65 +4609,65 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>32</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="K6" s="21" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>34</v>
@@ -4252,10 +4682,10 @@
         <v>10000000</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="I7" s="24" t="n">
         <f aca="false">IF(A7="","",E7-D7)</f>
@@ -4426,7 +4856,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J15" s="31" t="n">
         <f aca="false">SUM(J8:J14)</f>
@@ -4439,7 +4869,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -4476,31 +4906,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>34</v>
@@ -4641,7 +5071,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D20" s="31" t="n">
         <f aca="false">SUM(D6:D19)</f>
@@ -4684,25 +5114,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>49</v>
@@ -4720,18 +5150,18 @@
         <v>53</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>3000000</v>
@@ -4883,7 +5313,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -4893,123 +5323,123 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B5" s="28" t="n">
         <f aca="false">有価証券!H14</f>
         <v>20831200</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B6" s="28" t="n">
         <f aca="false">有価証券!H14-有価証券!I14</f>
         <v>6116000</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B7" s="28" t="n">
         <f aca="false">保険!J15</f>
         <v>0</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B8" s="28" t="n">
         <f aca="false">保険!J15-保険!K15</f>
         <v>0</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">預貯金!D20</f>
         <v>0</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B10" s="33" t="n">
         <f aca="false">有価証券!H14+保険!J15+預貯金!D20</f>
         <v>20831200</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B11" s="28" t="n">
         <f aca="false">有価証券!H14+保険!J15-有価証券!I14-保険!K15</f>
         <v>6116000</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B14" s="28" t="n">
-        <f aca="false">SUM(不動産!$R$6:$R$14)</f>
+        <f aca="false">SUM(不動産!$U$6:$U$14)</f>
         <v>0</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B15" s="28" t="n">
         <f aca="false">SUM(不動産!$F$6:$F$14)</f>
@@ -5019,19 +5449,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B16" s="28" t="n">
         <f aca="false">SUM(不動産!$G$6:$G$14)</f>
         <v>0</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B17" s="28" t="n">
         <f aca="false">SUM(不動産!$H$6:$H$14)</f>
@@ -5041,175 +5471,252 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B18" s="28" t="n">
-        <f aca="false">SUM(不動産!$S$6:$S$14)</f>
+        <f aca="false">SUM(不動産!$V$6:$V$14)</f>
         <v>0</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B19" s="34" t="n">
-        <f aca="false">IFERROR(SUM(不動産!$S$6:$S$14)/SUM(不動産!$G$6:$G$14),0)</f>
+        <f aca="false">IFERROR(SUM(不動産!$V$6:$V$14)/SUM(不動産!$G$6:$G$14),0)</f>
         <v>0</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B20" s="28" t="n">
-        <f aca="false">SUM(不動産!$U$6:$U$14)</f>
+        <f aca="false">SUM(不動産!$X$6:$X$14)</f>
         <v>0</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>146</v>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B21" s="28" t="n">
+        <f aca="false">IF(COUNT(不動産!$R$6:$R$14)=0,0,SUM(不動産!$R$6:$R$14))</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
-        <v>147</v>
+      <c r="A22" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="28" t="n">
+        <f aca="false">IF(COUNT(不動産!$R$6:$R$14)=0,0,SUM(不動産!$Z$6:$Z$14))</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="B23" s="28" t="n">
+      <c r="A23" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" s="34" t="n">
+        <f aca="false">IFERROR(SUM(不動産!$H$6:$H$14)/SUM(不動産!$R$6:$R$14),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" s="28" t="n">
         <f aca="false">SUM(不動産!$H$6:$H$14)</f>
         <v>0</v>
       </c>
-      <c r="C23" s="15"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="B24" s="28" t="n">
+      <c r="C26" s="15"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B27" s="28" t="n">
         <f aca="false">SUM(その他の借入!E7:E15)</f>
         <v>0</v>
       </c>
-      <c r="C24" s="15" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="32" t="s">
-        <v>151</v>
-      </c>
-      <c r="B25" s="33" t="n">
+      <c r="C27" s="15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="B28" s="33" t="n">
         <f aca="false">SUM(不動産!$H$6:$H$14)+SUM(その他の借入!E7:E15)</f>
         <v>0</v>
       </c>
-      <c r="C25" s="15" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
-        <v>154</v>
+      <c r="C28" s="15" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="B30" s="35" t="str">
+      <c r="A30" s="14" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B31" s="36" t="str">
+        <f aca="false">COUNT(不動産!$R$6:$R$14)&amp;" / "&amp;COUNTA(不動産!$A$6:$A$14)&amp;" 物件"</f>
+        <v>0 / 0 物件</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B32" s="28" t="n">
+        <f aca="false">IF(COUNT(不動産!$R$6:$R$14)&lt;&gt;COUNTA(不動産!$A$6:$A$14),"時価未入力あり",有価証券!H14+保険!J15+預貯金!D20+SUM(不動産!$R$6:$R$14))</f>
+        <v>20831200</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="B33" s="33" t="n">
+        <f aca="false">IF(COUNT(不動産!$R$6:$R$14)&lt;&gt;COUNTA(不動産!$A$6:$A$14),"時価未入力あり",有価証券!H14+保険!J15+預貯金!D20+SUM(不動産!$R$6:$R$14)-(SUM(不動産!$H$6:$H$14)+SUM(その他の借入!E7:E15)))</f>
+        <v>20831200</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="15" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B38" s="36" t="str">
         <f aca="false">IF(SUMPRODUCT((不動産!A6:A14&lt;&gt;"")*(不動産!H6:H14&gt;不動産!G6:G14))&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="B31" s="35" t="str">
+      <c r="C38" s="15" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B39" s="36" t="str">
         <f aca="false">IF(SUMPRODUCT((その他の借入!A7:A15&lt;&gt;"")*(その他の借入!E7:E15&gt;その他の借入!D7:D15))&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
-      <c r="C31" s="15" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="B32" s="35" t="str">
+      <c r="C39" s="15" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B40" s="36" t="str">
         <f aca="false">IF(SUMPRODUCT((不動産!F6:H14&lt;0)*1)+SUMPRODUCT((有価証券!D6:E13&lt;0)*1)&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
-      <c r="C32" s="15" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="B33" s="35" t="str">
+      <c r="C40" s="15" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B41" s="36" t="str">
         <f aca="false">IF(SUMPRODUCT(ISERROR(MATCH(有価証券!C6:C13,基本情報!$A$10:$A$13,0))*1)&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
-      <c r="C33" s="15" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="B34" s="35" t="str">
+      <c r="C41" s="15" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="B42" s="36" t="str">
         <f aca="false">IF(OR(基本情報!B4="",基本情報!B5=""),"要確認","OK")</f>
         <v>OK</v>
       </c>
-      <c r="C34" s="15" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="B35" s="35" t="str">
+      <c r="C42" s="15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B43" s="36" t="str">
         <f aca="false">IF(SUMPRODUCT((不動産!A6:A14&lt;&gt;"")*((不動産!L6:L14&lt;0)+(不動産!L6:L14&gt;11)))&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
-      <c r="C35" s="36" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="B36" s="35" t="str">
+      <c r="C43" s="37" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B44" s="36" t="str">
         <f aca="false">IF(SUMPRODUCT((保険!A8:A14&lt;&gt;"")*ISERROR(MATCH(保険!C8:C14,基本情報!$A$10:$A$13,0)))&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
-      <c r="C36" s="15" t="s">
-        <v>162</v>
+      <c r="C44" s="15" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B30:B36">
+  <conditionalFormatting sqref="B38:B44">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"要確認"</formula>
     </cfRule>

--- a/data/input-sheet.xlsx
+++ b/data/input-sheet.xlsx
@@ -44,7 +44,111 @@
         </r>
       </text>
     </comment>
+    <comment ref="I4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">今売ったらいくらか、の推定額です。空欄で構いません。全物件に入れると、①サマリーに総資産と純資産が出ます。</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">件でも空欄なら、純資産は出しません（実態より小さく出るため）。</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="K4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">その時価をどう出したか。例</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">不動産会社の査定書 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">/ </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">取引事例 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">/ </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">路線価から換算 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">/ </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">自己推定。空欄で構いませんが、書いておくと後から根拠をたどれます。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -184,7 +288,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0">
+    <comment ref="T4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -260,110 +364,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">今売ったらいくらか、の推定額です。空欄で構いません。全物件に入れると、①サマリーに総資産と純資産が出ます。</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">1</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">件でも空欄なら、純資産は出しません（実態より小さく出るため）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T4" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">その時価をどう出したか。例</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">不動産会社の査定書 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">/ </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">取引事例 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">/ </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">路線価から換算 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">/ </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">自己推定。空欄で構いませんが、書いておくと後から根拠をたどれます。</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -1148,6 +1148,141 @@
     <t xml:space="preserve">残債</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時価
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">任意</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">評価日
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">任意</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">評価の根拠
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">任意</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">借入先</t>
   </si>
   <si>
@@ -1484,16 +1619,21 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時価
-</t>
+    <t xml:space="preserve">総投資額</t>
+  </si>
+  <si>
+    <t xml:space="preserve">累計返済額</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">固定資産税</t>
     </r>
     <r>
       <rPr>
@@ -1514,7 +1654,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">任意</t>
+      <t xml:space="preserve">月</t>
     </r>
     <r>
       <rPr>
@@ -1529,16 +1669,18 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">評価日
-</t>
+    <t xml:space="preserve">月次収支</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">借入期間 合計</t>
     </r>
     <r>
       <rPr>
@@ -1559,7 +1701,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">任意</t>
+      <t xml:space="preserve">か月</t>
     </r>
     <r>
       <rPr>
@@ -1574,148 +1716,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">評価の根拠
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">任意</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">総投資額</t>
-  </si>
-  <si>
-    <t xml:space="preserve">累計返済額</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">固定資産税</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">月次収支</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">借入期間 合計</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">含み損益</t>
   </si>
   <si>
@@ -1768,6 +1768,12 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">2026-08-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不動産会社の査定書</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -1789,12 +1795,6 @@
       </rPr>
       <t xml:space="preserve">銀行</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不動産会社の査定書</t>
   </si>
   <si>
     <r>
@@ -3613,15 +3613,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="14"/>
@@ -3745,41 +3746,41 @@
       <c r="H5" s="24" t="n">
         <v>35500000</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="24" t="n">
+        <v>58000000</v>
+      </c>
+      <c r="J5" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="J5" s="25" t="n">
+      <c r="K5" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="M5" s="25" t="n">
         <v>1.8</v>
       </c>
-      <c r="K5" s="7" t="n">
+      <c r="N5" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="L5" s="7" t="n">
+      <c r="O5" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="M5" s="24" t="n">
+      <c r="P5" s="24" t="n">
         <v>128000</v>
       </c>
-      <c r="N5" s="24" t="n">
+      <c r="Q5" s="24" t="n">
         <v>180000</v>
       </c>
-      <c r="O5" s="24" t="n">
+      <c r="R5" s="24" t="n">
         <v>12000</v>
       </c>
-      <c r="P5" s="24" t="n">
+      <c r="S5" s="24" t="n">
         <v>8000</v>
       </c>
-      <c r="Q5" s="24" t="n">
+      <c r="T5" s="24" t="n">
         <v>108000</v>
-      </c>
-      <c r="R5" s="24" t="n">
-        <v>58000000</v>
-      </c>
-      <c r="S5" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="U5" s="24" t="n">
         <f aca="false">F5+G5</f>
@@ -3790,19 +3791,19 @@
         <v>4500000</v>
       </c>
       <c r="W5" s="24" t="n">
-        <f aca="false">ROUND(Q5/12,0)</f>
+        <f aca="false">ROUND(T5/12,0)</f>
         <v>9000</v>
       </c>
       <c r="X5" s="24" t="n">
-        <f aca="false">N5-M5-O5-P5-W5</f>
+        <f aca="false">Q5-P5-R5-S5-W5</f>
         <v>23000</v>
       </c>
       <c r="Y5" s="7" t="n">
-        <f aca="false">K5*12+L5</f>
+        <f aca="false">N5*12+O5</f>
         <v>323</v>
       </c>
       <c r="Z5" s="24" t="n">
-        <f aca="false">IF(R5="","",R5-U5)</f>
+        <f aca="false">IF(I5="","",I5-U5)</f>
         <v>8000000</v>
       </c>
     </row>
@@ -3815,18 +3816,18 @@
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
       <c r="H6" s="26"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="27"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="19"/>
       <c r="K6" s="19"/>
       <c r="L6" s="19"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
       <c r="P6" s="26"/>
       <c r="Q6" s="26"/>
       <c r="R6" s="26"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="19"/>
+      <c r="S6" s="26"/>
+      <c r="T6" s="26"/>
       <c r="U6" s="28" t="n">
         <f aca="false">F6+G6</f>
         <v>0</v>
@@ -3836,19 +3837,19 @@
         <v>0</v>
       </c>
       <c r="W6" s="28" t="n">
-        <f aca="false">ROUND(Q6/12,0)</f>
+        <f aca="false">ROUND(T6/12,0)</f>
         <v>0</v>
       </c>
       <c r="X6" s="28" t="n">
-        <f aca="false">N6-M6-O6-P6-W6</f>
+        <f aca="false">Q6-P6-R6-S6-W6</f>
         <v>0</v>
       </c>
       <c r="Y6" s="17" t="n">
-        <f aca="false">K6*12+L6</f>
+        <f aca="false">N6*12+O6</f>
         <v>0</v>
       </c>
       <c r="Z6" s="28" t="str">
-        <f aca="false">IF(R6="","",R6-U6)</f>
+        <f aca="false">IF(I6="","",I6-U6)</f>
         <v/>
       </c>
     </row>
@@ -3861,18 +3862,18 @@
       <c r="F7" s="26"/>
       <c r="G7" s="26"/>
       <c r="H7" s="26"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="27"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="19"/>
       <c r="K7" s="19"/>
       <c r="L7" s="19"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
       <c r="P7" s="26"/>
       <c r="Q7" s="26"/>
       <c r="R7" s="26"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
+      <c r="S7" s="26"/>
+      <c r="T7" s="26"/>
       <c r="U7" s="28" t="n">
         <f aca="false">F7+G7</f>
         <v>0</v>
@@ -3882,19 +3883,19 @@
         <v>0</v>
       </c>
       <c r="W7" s="28" t="n">
-        <f aca="false">ROUND(Q7/12,0)</f>
+        <f aca="false">ROUND(T7/12,0)</f>
         <v>0</v>
       </c>
       <c r="X7" s="28" t="n">
-        <f aca="false">N7-M7-O7-P7-W7</f>
+        <f aca="false">Q7-P7-R7-S7-W7</f>
         <v>0</v>
       </c>
       <c r="Y7" s="17" t="n">
-        <f aca="false">K7*12+L7</f>
+        <f aca="false">N7*12+O7</f>
         <v>0</v>
       </c>
       <c r="Z7" s="28" t="str">
-        <f aca="false">IF(R7="","",R7-U7)</f>
+        <f aca="false">IF(I7="","",I7-U7)</f>
         <v/>
       </c>
     </row>
@@ -3907,18 +3908,18 @@
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
       <c r="H8" s="26"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="27"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="19"/>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
       <c r="P8" s="26"/>
       <c r="Q8" s="26"/>
       <c r="R8" s="26"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
+      <c r="S8" s="26"/>
+      <c r="T8" s="26"/>
       <c r="U8" s="28" t="n">
         <f aca="false">F8+G8</f>
         <v>0</v>
@@ -3928,19 +3929,19 @@
         <v>0</v>
       </c>
       <c r="W8" s="28" t="n">
-        <f aca="false">ROUND(Q8/12,0)</f>
+        <f aca="false">ROUND(T8/12,0)</f>
         <v>0</v>
       </c>
       <c r="X8" s="28" t="n">
-        <f aca="false">N8-M8-O8-P8-W8</f>
+        <f aca="false">Q8-P8-R8-S8-W8</f>
         <v>0</v>
       </c>
       <c r="Y8" s="17" t="n">
-        <f aca="false">K8*12+L8</f>
+        <f aca="false">N8*12+O8</f>
         <v>0</v>
       </c>
       <c r="Z8" s="28" t="str">
-        <f aca="false">IF(R8="","",R8-U8)</f>
+        <f aca="false">IF(I8="","",I8-U8)</f>
         <v/>
       </c>
     </row>
@@ -3953,18 +3954,18 @@
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
       <c r="H9" s="26"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="27"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="19"/>
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
       <c r="P9" s="26"/>
       <c r="Q9" s="26"/>
       <c r="R9" s="26"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="26"/>
       <c r="U9" s="28" t="n">
         <f aca="false">F9+G9</f>
         <v>0</v>
@@ -3974,19 +3975,19 @@
         <v>0</v>
       </c>
       <c r="W9" s="28" t="n">
-        <f aca="false">ROUND(Q9/12,0)</f>
+        <f aca="false">ROUND(T9/12,0)</f>
         <v>0</v>
       </c>
       <c r="X9" s="28" t="n">
-        <f aca="false">N9-M9-O9-P9-W9</f>
+        <f aca="false">Q9-P9-R9-S9-W9</f>
         <v>0</v>
       </c>
       <c r="Y9" s="17" t="n">
-        <f aca="false">K9*12+L9</f>
+        <f aca="false">N9*12+O9</f>
         <v>0</v>
       </c>
       <c r="Z9" s="28" t="str">
-        <f aca="false">IF(R9="","",R9-U9)</f>
+        <f aca="false">IF(I9="","",I9-U9)</f>
         <v/>
       </c>
     </row>
@@ -3999,18 +4000,18 @@
       <c r="F10" s="26"/>
       <c r="G10" s="26"/>
       <c r="H10" s="26"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="27"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="19"/>
       <c r="K10" s="19"/>
       <c r="L10" s="19"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
       <c r="P10" s="26"/>
       <c r="Q10" s="26"/>
       <c r="R10" s="26"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
+      <c r="S10" s="26"/>
+      <c r="T10" s="26"/>
       <c r="U10" s="28" t="n">
         <f aca="false">F10+G10</f>
         <v>0</v>
@@ -4020,19 +4021,19 @@
         <v>0</v>
       </c>
       <c r="W10" s="28" t="n">
-        <f aca="false">ROUND(Q10/12,0)</f>
+        <f aca="false">ROUND(T10/12,0)</f>
         <v>0</v>
       </c>
       <c r="X10" s="28" t="n">
-        <f aca="false">N10-M10-O10-P10-W10</f>
+        <f aca="false">Q10-P10-R10-S10-W10</f>
         <v>0</v>
       </c>
       <c r="Y10" s="17" t="n">
-        <f aca="false">K10*12+L10</f>
+        <f aca="false">N10*12+O10</f>
         <v>0</v>
       </c>
       <c r="Z10" s="28" t="str">
-        <f aca="false">IF(R10="","",R10-U10)</f>
+        <f aca="false">IF(I10="","",I10-U10)</f>
         <v/>
       </c>
     </row>
@@ -4045,18 +4046,18 @@
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
       <c r="H11" s="26"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="27"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="19"/>
       <c r="K11" s="19"/>
       <c r="L11" s="19"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
       <c r="P11" s="26"/>
       <c r="Q11" s="26"/>
       <c r="R11" s="26"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
+      <c r="S11" s="26"/>
+      <c r="T11" s="26"/>
       <c r="U11" s="28" t="n">
         <f aca="false">F11+G11</f>
         <v>0</v>
@@ -4066,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="W11" s="28" t="n">
-        <f aca="false">ROUND(Q11/12,0)</f>
+        <f aca="false">ROUND(T11/12,0)</f>
         <v>0</v>
       </c>
       <c r="X11" s="28" t="n">
-        <f aca="false">N11-M11-O11-P11-W11</f>
+        <f aca="false">Q11-P11-R11-S11-W11</f>
         <v>0</v>
       </c>
       <c r="Y11" s="17" t="n">
-        <f aca="false">K11*12+L11</f>
+        <f aca="false">N11*12+O11</f>
         <v>0</v>
       </c>
       <c r="Z11" s="28" t="str">
-        <f aca="false">IF(R11="","",R11-U11)</f>
+        <f aca="false">IF(I11="","",I11-U11)</f>
         <v/>
       </c>
     </row>
@@ -4091,18 +4092,18 @@
       <c r="F12" s="26"/>
       <c r="G12" s="26"/>
       <c r="H12" s="26"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="27"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="19"/>
       <c r="K12" s="19"/>
       <c r="L12" s="19"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
-      <c r="O12" s="26"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
       <c r="P12" s="26"/>
       <c r="Q12" s="26"/>
       <c r="R12" s="26"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="19"/>
+      <c r="S12" s="26"/>
+      <c r="T12" s="26"/>
       <c r="U12" s="28" t="n">
         <f aca="false">F12+G12</f>
         <v>0</v>
@@ -4112,19 +4113,19 @@
         <v>0</v>
       </c>
       <c r="W12" s="28" t="n">
-        <f aca="false">ROUND(Q12/12,0)</f>
+        <f aca="false">ROUND(T12/12,0)</f>
         <v>0</v>
       </c>
       <c r="X12" s="28" t="n">
-        <f aca="false">N12-M12-O12-P12-W12</f>
+        <f aca="false">Q12-P12-R12-S12-W12</f>
         <v>0</v>
       </c>
       <c r="Y12" s="17" t="n">
-        <f aca="false">K12*12+L12</f>
+        <f aca="false">N12*12+O12</f>
         <v>0</v>
       </c>
       <c r="Z12" s="28" t="str">
-        <f aca="false">IF(R12="","",R12-U12)</f>
+        <f aca="false">IF(I12="","",I12-U12)</f>
         <v/>
       </c>
     </row>
@@ -4137,18 +4138,18 @@
       <c r="F13" s="26"/>
       <c r="G13" s="26"/>
       <c r="H13" s="26"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="27"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="19"/>
       <c r="K13" s="19"/>
       <c r="L13" s="19"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="26"/>
-      <c r="O13" s="26"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
       <c r="P13" s="26"/>
       <c r="Q13" s="26"/>
       <c r="R13" s="26"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
+      <c r="S13" s="26"/>
+      <c r="T13" s="26"/>
       <c r="U13" s="28" t="n">
         <f aca="false">F13+G13</f>
         <v>0</v>
@@ -4158,19 +4159,19 @@
         <v>0</v>
       </c>
       <c r="W13" s="28" t="n">
-        <f aca="false">ROUND(Q13/12,0)</f>
+        <f aca="false">ROUND(T13/12,0)</f>
         <v>0</v>
       </c>
       <c r="X13" s="28" t="n">
-        <f aca="false">N13-M13-O13-P13-W13</f>
+        <f aca="false">Q13-P13-R13-S13-W13</f>
         <v>0</v>
       </c>
       <c r="Y13" s="17" t="n">
-        <f aca="false">K13*12+L13</f>
+        <f aca="false">N13*12+O13</f>
         <v>0</v>
       </c>
       <c r="Z13" s="28" t="str">
-        <f aca="false">IF(R13="","",R13-U13)</f>
+        <f aca="false">IF(I13="","",I13-U13)</f>
         <v/>
       </c>
     </row>
@@ -4183,18 +4184,18 @@
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
       <c r="H14" s="26"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="27"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="19"/>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="26"/>
-      <c r="O14" s="26"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
       <c r="P14" s="26"/>
       <c r="Q14" s="26"/>
       <c r="R14" s="26"/>
-      <c r="S14" s="19"/>
-      <c r="T14" s="19"/>
+      <c r="S14" s="26"/>
+      <c r="T14" s="26"/>
       <c r="U14" s="28" t="n">
         <f aca="false">F14+G14</f>
         <v>0</v>
@@ -4204,19 +4205,19 @@
         <v>0</v>
       </c>
       <c r="W14" s="28" t="n">
-        <f aca="false">ROUND(Q14/12,0)</f>
+        <f aca="false">ROUND(T14/12,0)</f>
         <v>0</v>
       </c>
       <c r="X14" s="28" t="n">
-        <f aca="false">N14-M14-O14-P14-W14</f>
+        <f aca="false">Q14-P14-R14-S14-W14</f>
         <v>0</v>
       </c>
       <c r="Y14" s="17" t="n">
-        <f aca="false">K14*12+L14</f>
+        <f aca="false">N14*12+O14</f>
         <v>0</v>
       </c>
       <c r="Z14" s="28" t="str">
-        <f aca="false">IF(R14="","",R14-U14)</f>
+        <f aca="false">IF(I14="","",I14-U14)</f>
         <v/>
       </c>
     </row>
@@ -5135,7 +5136,7 @@
         <v>78</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>47</v>
@@ -5144,10 +5145,10 @@
         <v>48</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H5" s="21" t="s">
         <v>122</v>
@@ -5510,7 +5511,7 @@
         <v>152</v>
       </c>
       <c r="B21" s="28" t="n">
-        <f aca="false">IF(COUNT(不動産!$R$6:$R$14)=0,0,SUM(不動産!$R$6:$R$14))</f>
+        <f aca="false">IF(COUNT(不動産!$I$6:$I$14)=0,0,SUM(不動産!$I$6:$I$14))</f>
         <v>0</v>
       </c>
       <c r="C21" s="15" t="s">
@@ -5522,7 +5523,7 @@
         <v>131</v>
       </c>
       <c r="B22" s="28" t="n">
-        <f aca="false">IF(COUNT(不動産!$R$6:$R$14)=0,0,SUM(不動産!$Z$6:$Z$14))</f>
+        <f aca="false">IF(COUNT(不動産!$I$6:$I$14)=0,0,SUM(不動産!$Z$6:$Z$14))</f>
         <v>0</v>
       </c>
       <c r="C22" s="15" t="s">
@@ -5534,7 +5535,7 @@
         <v>155</v>
       </c>
       <c r="B23" s="34" t="n">
-        <f aca="false">IFERROR(SUM(不動産!$H$6:$H$14)/SUM(不動産!$R$6:$R$14),0)</f>
+        <f aca="false">IFERROR(SUM(不動産!$H$6:$H$14)/SUM(不動産!$I$6:$I$14),0)</f>
         <v>0</v>
       </c>
       <c r="C23" s="15" t="s">
@@ -5590,7 +5591,7 @@
         <v>164</v>
       </c>
       <c r="B31" s="36" t="str">
-        <f aca="false">COUNT(不動産!$R$6:$R$14)&amp;" / "&amp;COUNTA(不動産!$A$6:$A$14)&amp;" 物件"</f>
+        <f aca="false">COUNT(不動産!$I$6:$I$14)&amp;" / "&amp;COUNTA(不動産!$A$6:$A$14)&amp;" 物件"</f>
         <v>0 / 0 物件</v>
       </c>
       <c r="C31" s="12" t="s">
@@ -5602,7 +5603,7 @@
         <v>166</v>
       </c>
       <c r="B32" s="28" t="n">
-        <f aca="false">IF(COUNT(不動産!$R$6:$R$14)&lt;&gt;COUNTA(不動産!$A$6:$A$14),"時価未入力あり",有価証券!H14+保険!J15+預貯金!D20+SUM(不動産!$R$6:$R$14))</f>
+        <f aca="false">IF(COUNT(不動産!$I$6:$I$14)&lt;&gt;COUNTA(不動産!$A$6:$A$14),"時価未入力あり",有価証券!H14+保険!J15+預貯金!D20+SUM(不動産!$I$6:$I$14))</f>
         <v>20831200</v>
       </c>
       <c r="C32" s="12" t="s">
@@ -5614,7 +5615,7 @@
         <v>168</v>
       </c>
       <c r="B33" s="33" t="n">
-        <f aca="false">IF(COUNT(不動産!$R$6:$R$14)&lt;&gt;COUNTA(不動産!$A$6:$A$14),"時価未入力あり",有価証券!H14+保険!J15+預貯金!D20+SUM(不動産!$R$6:$R$14)-(SUM(不動産!$H$6:$H$14)+SUM(その他の借入!E7:E15)))</f>
+        <f aca="false">IF(COUNT(不動産!$I$6:$I$14)&lt;&gt;COUNTA(不動産!$A$6:$A$14),"時価未入力あり",有価証券!H14+保険!J15+預貯金!D20+SUM(不動産!$I$6:$I$14)-(SUM(不動産!$H$6:$H$14)+SUM(その他の借入!E7:E15)))</f>
         <v>20831200</v>
       </c>
       <c r="C33" s="12" t="s">
@@ -5696,7 +5697,7 @@
         <v>182</v>
       </c>
       <c r="B43" s="36" t="str">
-        <f aca="false">IF(SUMPRODUCT((不動産!A6:A14&lt;&gt;"")*((不動産!L6:L14&lt;0)+(不動産!L6:L14&gt;11)))&gt;0,"要確認","OK")</f>
+        <f aca="false">IF(SUMPRODUCT((不動産!A6:A14&lt;&gt;"")*((不動産!O6:O14&lt;0)+(不動産!O6:O14&gt;11)))&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
       <c r="C43" s="37" t="s">

--- a/data/input-sheet.xlsx
+++ b/data/input-sheet.xlsx
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="187">
   <si>
     <t xml:space="preserve">資産ダッシュボード 入力シート</t>
   </si>
@@ -2709,6 +2709,12 @@
       </rPr>
       <t xml:space="preserve">か月以上は「年」の側に繰り上げてください</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">時価が残債を下回る物件</t>
+  </si>
+  <si>
+    <t xml:space="preserve">時価が借入残高より小さい状態です。桁や利回りの計算を確かめてください</t>
   </si>
   <si>
     <t xml:space="preserve">保険にレートの無い通貨がある</t>
@@ -5314,7 +5320,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -5692,7 +5698,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
         <v>182</v>
       </c>
@@ -5709,15 +5715,27 @@
         <v>184</v>
       </c>
       <c r="B44" s="36" t="str">
+        <f aca="false">IF(SUMPRODUCT((不動産!A6:A14&lt;&gt;"")*(不動産!I6:I14&gt;0)*(不動産!I6:I14&lt;不動産!H6:H14))&gt;0,"要確認","OK")</f>
+        <v>OK</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B45" s="36" t="str">
         <f aca="false">IF(SUMPRODUCT((保険!A8:A14&lt;&gt;"")*ISERROR(MATCH(保険!C8:C14,基本情報!$A$10:$A$13,0)))&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C45" s="15" t="s">
         <v>179</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B38:B44">
+  <conditionalFormatting sqref="B38:B45">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"要確認"</formula>
     </cfRule>

--- a/data/input-sheet.xlsx
+++ b/data/input-sheet.xlsx
@@ -52,7 +52,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">今売ったらいくらか、の推定額です。空欄で構いません。全物件に入れると、①サマリーに総資産と純資産が出ます。</t>
+          <t xml:space="preserve">今売ったらいくらか、の推定額です。空欄で構いません。右の「月間総収入」と「実質利回り」を入れると収益還元法で自動計算します。査定書などの金額を直接入れたいときは、この欄に数字を上書きしてください。全物件に入れると①サマリーに総資産と純資産が出ます。</t>
         </r>
         <r>
           <rPr>
@@ -68,7 +68,83 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">件でも空欄なら、純資産は出しません（実態より小さく出るため）。</t>
+          <t xml:space="preserve">件でも空欄なら出しません。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">収益還元法で時価を出すときの、</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">か月あたりの総収入（満室想定）です。共益費などを含む場合は「家賃収入</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">月</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">)</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">」と違う金額になって構いません。ここから管理費と修繕積立金を引いて</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">12</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">倍し、年間の純収益にします。</t>
         </r>
       </text>
     </comment>
@@ -80,7 +156,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">その時価をどう出したか。例</t>
+          <t xml:space="preserve">実質利回りを </t>
         </r>
         <r>
           <rPr>
@@ -88,7 +164,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">: </t>
+          <t xml:space="preserve">% </t>
         </r>
         <r>
           <rPr>
@@ -96,7 +172,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">不動産会社の査定書 </t>
+          <t xml:space="preserve">のまま入れてください。</t>
         </r>
         <r>
           <rPr>
@@ -104,7 +180,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">/ </t>
+          <t xml:space="preserve">4% </t>
         </r>
         <r>
           <rPr>
@@ -112,7 +188,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">取引事例 </t>
+          <t xml:space="preserve">なら「</t>
         </r>
         <r>
           <rPr>
@@ -120,7 +196,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">/ </t>
+          <t xml:space="preserve">4</t>
         </r>
         <r>
           <rPr>
@@ -128,7 +204,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">路線価から換算 </t>
+          <t xml:space="preserve">」、</t>
         </r>
         <r>
           <rPr>
@@ -136,7 +212,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">/ </t>
+          <t xml:space="preserve">3.5% </t>
         </r>
         <r>
           <rPr>
@@ -144,11 +220,59 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">自己推定。空欄で構いませんが、書いておくと後から根拠をたどれます。</t>
+          <t xml:space="preserve">なら「</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">3.5</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">」です。</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">0.04 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">のように小数で入れる必要はありません（シートが</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">100</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">で割ります）。</t>
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0">
+    <comment ref="M4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -156,7 +280,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">契約したときの期間です（残りの期間ではありません）。</t>
+          <t xml:space="preserve">その時価をどう出したか。例</t>
         </r>
         <r>
           <rPr>
@@ -164,7 +288,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">: </t>
         </r>
         <r>
           <rPr>
@@ -172,7 +296,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">年</t>
+          <t xml:space="preserve">不動産会社の査定書 </t>
         </r>
         <r>
           <rPr>
@@ -180,7 +304,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">/ </t>
         </r>
         <r>
           <rPr>
@@ -188,7 +312,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">か月なら「年」に </t>
+          <t xml:space="preserve">取引事例 </t>
         </r>
         <r>
           <rPr>
@@ -196,7 +320,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">/ </t>
         </r>
         <r>
           <rPr>
@@ -204,7 +328,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">、「か月」に </t>
+          <t xml:space="preserve">路線価から換算 </t>
         </r>
         <r>
           <rPr>
@@ -212,7 +336,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">/ </t>
         </r>
         <r>
           <rPr>
@@ -220,75 +344,151 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">。ちょうど</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">20</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">年なら </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">20 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">と </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">0</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">。返済回数しか分からないときは </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">12 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">で割った商と余りを入れてください。</t>
+          <t xml:space="preserve">自己推定。空欄で構いませんが、書いておくと後から根拠をたどれます。</t>
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="0">
+    <comment ref="P4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">契約したときの期間です（残りの期間ではありません）。</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">26</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">年</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">11</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">か月なら「年」に </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">26</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">、「か月」に </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">11</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">。ちょうど</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">20</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">年なら </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">20 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">と </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">0</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">。返済回数しか分からないときは </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">12 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">で割った商と余りを入れてください。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -425,7 +625,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="189">
   <si>
     <t xml:space="preserve">資産ダッシュボード 入力シート</t>
   </si>
@@ -1148,15 +1348,63 @@
     <t xml:space="preserve">残債</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時価
+    <t xml:space="preserve">時価</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月間総収入
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">任意</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実質利回り
 </t>
     </r>
     <r>
@@ -1771,7 +2019,7 @@
     <t xml:space="preserve">2026-08-01</t>
   </si>
   <si>
-    <t xml:space="preserve">不動産会社の査定書</t>
+    <t xml:space="preserve">収益還元法</t>
   </si>
   <si>
     <r>
@@ -3610,7 +3858,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:AB16"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -3620,21 +3868,23 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3726,19 +3976,25 @@
       <c r="Z4" s="21" t="s">
         <v>66</v>
       </c>
+      <c r="AA4" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB4" s="21" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C5" s="22" t="n">
         <v>45.5</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>15</v>
@@ -3753,64 +4009,71 @@
         <v>35500000</v>
       </c>
       <c r="I5" s="24" t="n">
-        <v>58000000</v>
-      </c>
-      <c r="J5" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>71</v>
+        <f aca="false">IF(OR(J5="",K5=""),"",ROUND((J5-T5-U5)*12/(K5/100),0))</f>
+        <v>54000000</v>
+      </c>
+      <c r="J5" s="24" t="n">
+        <v>200000</v>
+      </c>
+      <c r="K5" s="25" t="n">
+        <v>4</v>
       </c>
       <c r="L5" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="M5" s="25" t="n">
+      <c r="M5" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="N5" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="O5" s="25" t="n">
         <v>1.8</v>
       </c>
-      <c r="N5" s="7" t="n">
+      <c r="P5" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="O5" s="7" t="n">
+      <c r="Q5" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="P5" s="24" t="n">
+      <c r="R5" s="24" t="n">
         <v>128000</v>
       </c>
-      <c r="Q5" s="24" t="n">
+      <c r="S5" s="24" t="n">
         <v>180000</v>
       </c>
-      <c r="R5" s="24" t="n">
+      <c r="T5" s="24" t="n">
         <v>12000</v>
       </c>
-      <c r="S5" s="24" t="n">
+      <c r="U5" s="24" t="n">
         <v>8000</v>
       </c>
-      <c r="T5" s="24" t="n">
+      <c r="V5" s="24" t="n">
         <v>108000</v>
       </c>
-      <c r="U5" s="24" t="n">
+      <c r="W5" s="24" t="n">
         <f aca="false">F5+G5</f>
         <v>50000000</v>
       </c>
-      <c r="V5" s="24" t="n">
+      <c r="X5" s="24" t="n">
         <f aca="false">G5-H5</f>
         <v>4500000</v>
       </c>
-      <c r="W5" s="24" t="n">
-        <f aca="false">ROUND(T5/12,0)</f>
+      <c r="Y5" s="24" t="n">
+        <f aca="false">ROUND(V5/12,0)</f>
         <v>9000</v>
       </c>
-      <c r="X5" s="24" t="n">
-        <f aca="false">Q5-P5-R5-S5-W5</f>
+      <c r="Z5" s="24" t="n">
+        <f aca="false">S5-R5-T5-U5-Y5</f>
         <v>23000</v>
       </c>
-      <c r="Y5" s="7" t="n">
-        <f aca="false">N5*12+O5</f>
+      <c r="AA5" s="7" t="n">
+        <f aca="false">P5*12+Q5</f>
         <v>323</v>
       </c>
-      <c r="Z5" s="24" t="n">
-        <f aca="false">IF(I5="","",I5-U5)</f>
-        <v>8000000</v>
+      <c r="AB5" s="24" t="n">
+        <f aca="false">IF(I5="","",I5-W5)</f>
+        <v>4000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3822,40 +4085,45 @@
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
       <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
+      <c r="I6" s="26" t="str">
+        <f aca="false">IF(OR(J6="",K6=""),"",ROUND((J6-T6-U6)*12/(K6/100),0))</f>
+        <v/>
+      </c>
+      <c r="J6" s="26"/>
+      <c r="K6" s="27"/>
       <c r="L6" s="19"/>
-      <c r="M6" s="27"/>
+      <c r="M6" s="19"/>
       <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="26"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
       <c r="R6" s="26"/>
       <c r="S6" s="26"/>
       <c r="T6" s="26"/>
-      <c r="U6" s="28" t="n">
+      <c r="U6" s="26"/>
+      <c r="V6" s="26"/>
+      <c r="W6" s="28" t="n">
         <f aca="false">F6+G6</f>
         <v>0</v>
       </c>
-      <c r="V6" s="28" t="n">
+      <c r="X6" s="28" t="n">
         <f aca="false">G6-H6</f>
         <v>0</v>
       </c>
-      <c r="W6" s="28" t="n">
-        <f aca="false">ROUND(T6/12,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X6" s="28" t="n">
-        <f aca="false">Q6-P6-R6-S6-W6</f>
-        <v>0</v>
-      </c>
-      <c r="Y6" s="17" t="n">
-        <f aca="false">N6*12+O6</f>
-        <v>0</v>
-      </c>
-      <c r="Z6" s="28" t="str">
-        <f aca="false">IF(I6="","",I6-U6)</f>
+      <c r="Y6" s="28" t="n">
+        <f aca="false">ROUND(V6/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="28" t="n">
+        <f aca="false">S6-R6-T6-U6-Y6</f>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="17" t="n">
+        <f aca="false">P6*12+Q6</f>
+        <v>0</v>
+      </c>
+      <c r="AB6" s="28" t="str">
+        <f aca="false">IF(I6="","",I6-W6)</f>
         <v/>
       </c>
     </row>
@@ -3868,40 +4136,45 @@
       <c r="F7" s="26"/>
       <c r="G7" s="26"/>
       <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
+      <c r="I7" s="26" t="str">
+        <f aca="false">IF(OR(J7="",K7=""),"",ROUND((J7-T7-U7)*12/(K7/100),0))</f>
+        <v/>
+      </c>
+      <c r="J7" s="26"/>
+      <c r="K7" s="27"/>
       <c r="L7" s="19"/>
-      <c r="M7" s="27"/>
+      <c r="M7" s="19"/>
       <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="26"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
       <c r="R7" s="26"/>
       <c r="S7" s="26"/>
       <c r="T7" s="26"/>
-      <c r="U7" s="28" t="n">
+      <c r="U7" s="26"/>
+      <c r="V7" s="26"/>
+      <c r="W7" s="28" t="n">
         <f aca="false">F7+G7</f>
         <v>0</v>
       </c>
-      <c r="V7" s="28" t="n">
+      <c r="X7" s="28" t="n">
         <f aca="false">G7-H7</f>
         <v>0</v>
       </c>
-      <c r="W7" s="28" t="n">
-        <f aca="false">ROUND(T7/12,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X7" s="28" t="n">
-        <f aca="false">Q7-P7-R7-S7-W7</f>
-        <v>0</v>
-      </c>
-      <c r="Y7" s="17" t="n">
-        <f aca="false">N7*12+O7</f>
-        <v>0</v>
-      </c>
-      <c r="Z7" s="28" t="str">
-        <f aca="false">IF(I7="","",I7-U7)</f>
+      <c r="Y7" s="28" t="n">
+        <f aca="false">ROUND(V7/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="28" t="n">
+        <f aca="false">S7-R7-T7-U7-Y7</f>
+        <v>0</v>
+      </c>
+      <c r="AA7" s="17" t="n">
+        <f aca="false">P7*12+Q7</f>
+        <v>0</v>
+      </c>
+      <c r="AB7" s="28" t="str">
+        <f aca="false">IF(I7="","",I7-W7)</f>
         <v/>
       </c>
     </row>
@@ -3914,40 +4187,45 @@
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
       <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
+      <c r="I8" s="26" t="str">
+        <f aca="false">IF(OR(J8="",K8=""),"",ROUND((J8-T8-U8)*12/(K8/100),0))</f>
+        <v/>
+      </c>
+      <c r="J8" s="26"/>
+      <c r="K8" s="27"/>
       <c r="L8" s="19"/>
-      <c r="M8" s="27"/>
+      <c r="M8" s="19"/>
       <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
       <c r="R8" s="26"/>
       <c r="S8" s="26"/>
       <c r="T8" s="26"/>
-      <c r="U8" s="28" t="n">
+      <c r="U8" s="26"/>
+      <c r="V8" s="26"/>
+      <c r="W8" s="28" t="n">
         <f aca="false">F8+G8</f>
         <v>0</v>
       </c>
-      <c r="V8" s="28" t="n">
+      <c r="X8" s="28" t="n">
         <f aca="false">G8-H8</f>
         <v>0</v>
       </c>
-      <c r="W8" s="28" t="n">
-        <f aca="false">ROUND(T8/12,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X8" s="28" t="n">
-        <f aca="false">Q8-P8-R8-S8-W8</f>
-        <v>0</v>
-      </c>
-      <c r="Y8" s="17" t="n">
-        <f aca="false">N8*12+O8</f>
-        <v>0</v>
-      </c>
-      <c r="Z8" s="28" t="str">
-        <f aca="false">IF(I8="","",I8-U8)</f>
+      <c r="Y8" s="28" t="n">
+        <f aca="false">ROUND(V8/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="28" t="n">
+        <f aca="false">S8-R8-T8-U8-Y8</f>
+        <v>0</v>
+      </c>
+      <c r="AA8" s="17" t="n">
+        <f aca="false">P8*12+Q8</f>
+        <v>0</v>
+      </c>
+      <c r="AB8" s="28" t="str">
+        <f aca="false">IF(I8="","",I8-W8)</f>
         <v/>
       </c>
     </row>
@@ -3960,40 +4238,45 @@
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
       <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
+      <c r="I9" s="26" t="str">
+        <f aca="false">IF(OR(J9="",K9=""),"",ROUND((J9-T9-U9)*12/(K9/100),0))</f>
+        <v/>
+      </c>
+      <c r="J9" s="26"/>
+      <c r="K9" s="27"/>
       <c r="L9" s="19"/>
-      <c r="M9" s="27"/>
+      <c r="M9" s="19"/>
       <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
       <c r="R9" s="26"/>
       <c r="S9" s="26"/>
       <c r="T9" s="26"/>
-      <c r="U9" s="28" t="n">
+      <c r="U9" s="26"/>
+      <c r="V9" s="26"/>
+      <c r="W9" s="28" t="n">
         <f aca="false">F9+G9</f>
         <v>0</v>
       </c>
-      <c r="V9" s="28" t="n">
+      <c r="X9" s="28" t="n">
         <f aca="false">G9-H9</f>
         <v>0</v>
       </c>
-      <c r="W9" s="28" t="n">
-        <f aca="false">ROUND(T9/12,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X9" s="28" t="n">
-        <f aca="false">Q9-P9-R9-S9-W9</f>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="17" t="n">
-        <f aca="false">N9*12+O9</f>
-        <v>0</v>
-      </c>
-      <c r="Z9" s="28" t="str">
-        <f aca="false">IF(I9="","",I9-U9)</f>
+      <c r="Y9" s="28" t="n">
+        <f aca="false">ROUND(V9/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="28" t="n">
+        <f aca="false">S9-R9-T9-U9-Y9</f>
+        <v>0</v>
+      </c>
+      <c r="AA9" s="17" t="n">
+        <f aca="false">P9*12+Q9</f>
+        <v>0</v>
+      </c>
+      <c r="AB9" s="28" t="str">
+        <f aca="false">IF(I9="","",I9-W9)</f>
         <v/>
       </c>
     </row>
@@ -4006,40 +4289,45 @@
       <c r="F10" s="26"/>
       <c r="G10" s="26"/>
       <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
+      <c r="I10" s="26" t="str">
+        <f aca="false">IF(OR(J10="",K10=""),"",ROUND((J10-T10-U10)*12/(K10/100),0))</f>
+        <v/>
+      </c>
+      <c r="J10" s="26"/>
+      <c r="K10" s="27"/>
       <c r="L10" s="19"/>
-      <c r="M10" s="27"/>
+      <c r="M10" s="19"/>
       <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="26"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
       <c r="R10" s="26"/>
       <c r="S10" s="26"/>
       <c r="T10" s="26"/>
-      <c r="U10" s="28" t="n">
+      <c r="U10" s="26"/>
+      <c r="V10" s="26"/>
+      <c r="W10" s="28" t="n">
         <f aca="false">F10+G10</f>
         <v>0</v>
       </c>
-      <c r="V10" s="28" t="n">
+      <c r="X10" s="28" t="n">
         <f aca="false">G10-H10</f>
         <v>0</v>
       </c>
-      <c r="W10" s="28" t="n">
-        <f aca="false">ROUND(T10/12,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X10" s="28" t="n">
-        <f aca="false">Q10-P10-R10-S10-W10</f>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="17" t="n">
-        <f aca="false">N10*12+O10</f>
-        <v>0</v>
-      </c>
-      <c r="Z10" s="28" t="str">
-        <f aca="false">IF(I10="","",I10-U10)</f>
+      <c r="Y10" s="28" t="n">
+        <f aca="false">ROUND(V10/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="28" t="n">
+        <f aca="false">S10-R10-T10-U10-Y10</f>
+        <v>0</v>
+      </c>
+      <c r="AA10" s="17" t="n">
+        <f aca="false">P10*12+Q10</f>
+        <v>0</v>
+      </c>
+      <c r="AB10" s="28" t="str">
+        <f aca="false">IF(I10="","",I10-W10)</f>
         <v/>
       </c>
     </row>
@@ -4052,40 +4340,45 @@
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
       <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
+      <c r="I11" s="26" t="str">
+        <f aca="false">IF(OR(J11="",K11=""),"",ROUND((J11-T11-U11)*12/(K11/100),0))</f>
+        <v/>
+      </c>
+      <c r="J11" s="26"/>
+      <c r="K11" s="27"/>
       <c r="L11" s="19"/>
-      <c r="M11" s="27"/>
+      <c r="M11" s="19"/>
       <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="26"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
       <c r="R11" s="26"/>
       <c r="S11" s="26"/>
       <c r="T11" s="26"/>
-      <c r="U11" s="28" t="n">
+      <c r="U11" s="26"/>
+      <c r="V11" s="26"/>
+      <c r="W11" s="28" t="n">
         <f aca="false">F11+G11</f>
         <v>0</v>
       </c>
-      <c r="V11" s="28" t="n">
+      <c r="X11" s="28" t="n">
         <f aca="false">G11-H11</f>
         <v>0</v>
       </c>
-      <c r="W11" s="28" t="n">
-        <f aca="false">ROUND(T11/12,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X11" s="28" t="n">
-        <f aca="false">Q11-P11-R11-S11-W11</f>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="17" t="n">
-        <f aca="false">N11*12+O11</f>
-        <v>0</v>
-      </c>
-      <c r="Z11" s="28" t="str">
-        <f aca="false">IF(I11="","",I11-U11)</f>
+      <c r="Y11" s="28" t="n">
+        <f aca="false">ROUND(V11/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="28" t="n">
+        <f aca="false">S11-R11-T11-U11-Y11</f>
+        <v>0</v>
+      </c>
+      <c r="AA11" s="17" t="n">
+        <f aca="false">P11*12+Q11</f>
+        <v>0</v>
+      </c>
+      <c r="AB11" s="28" t="str">
+        <f aca="false">IF(I11="","",I11-W11)</f>
         <v/>
       </c>
     </row>
@@ -4098,40 +4391,45 @@
       <c r="F12" s="26"/>
       <c r="G12" s="26"/>
       <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
+      <c r="I12" s="26" t="str">
+        <f aca="false">IF(OR(J12="",K12=""),"",ROUND((J12-T12-U12)*12/(K12/100),0))</f>
+        <v/>
+      </c>
+      <c r="J12" s="26"/>
+      <c r="K12" s="27"/>
       <c r="L12" s="19"/>
-      <c r="M12" s="27"/>
+      <c r="M12" s="19"/>
       <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="26"/>
-      <c r="Q12" s="26"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
       <c r="R12" s="26"/>
       <c r="S12" s="26"/>
       <c r="T12" s="26"/>
-      <c r="U12" s="28" t="n">
+      <c r="U12" s="26"/>
+      <c r="V12" s="26"/>
+      <c r="W12" s="28" t="n">
         <f aca="false">F12+G12</f>
         <v>0</v>
       </c>
-      <c r="V12" s="28" t="n">
+      <c r="X12" s="28" t="n">
         <f aca="false">G12-H12</f>
         <v>0</v>
       </c>
-      <c r="W12" s="28" t="n">
-        <f aca="false">ROUND(T12/12,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X12" s="28" t="n">
-        <f aca="false">Q12-P12-R12-S12-W12</f>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="17" t="n">
-        <f aca="false">N12*12+O12</f>
-        <v>0</v>
-      </c>
-      <c r="Z12" s="28" t="str">
-        <f aca="false">IF(I12="","",I12-U12)</f>
+      <c r="Y12" s="28" t="n">
+        <f aca="false">ROUND(V12/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="28" t="n">
+        <f aca="false">S12-R12-T12-U12-Y12</f>
+        <v>0</v>
+      </c>
+      <c r="AA12" s="17" t="n">
+        <f aca="false">P12*12+Q12</f>
+        <v>0</v>
+      </c>
+      <c r="AB12" s="28" t="str">
+        <f aca="false">IF(I12="","",I12-W12)</f>
         <v/>
       </c>
     </row>
@@ -4144,40 +4442,45 @@
       <c r="F13" s="26"/>
       <c r="G13" s="26"/>
       <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
+      <c r="I13" s="26" t="str">
+        <f aca="false">IF(OR(J13="",K13=""),"",ROUND((J13-T13-U13)*12/(K13/100),0))</f>
+        <v/>
+      </c>
+      <c r="J13" s="26"/>
+      <c r="K13" s="27"/>
       <c r="L13" s="19"/>
-      <c r="M13" s="27"/>
+      <c r="M13" s="19"/>
       <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="26"/>
-      <c r="Q13" s="26"/>
+      <c r="O13" s="27"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
       <c r="R13" s="26"/>
       <c r="S13" s="26"/>
       <c r="T13" s="26"/>
-      <c r="U13" s="28" t="n">
+      <c r="U13" s="26"/>
+      <c r="V13" s="26"/>
+      <c r="W13" s="28" t="n">
         <f aca="false">F13+G13</f>
         <v>0</v>
       </c>
-      <c r="V13" s="28" t="n">
+      <c r="X13" s="28" t="n">
         <f aca="false">G13-H13</f>
         <v>0</v>
       </c>
-      <c r="W13" s="28" t="n">
-        <f aca="false">ROUND(T13/12,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X13" s="28" t="n">
-        <f aca="false">Q13-P13-R13-S13-W13</f>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="17" t="n">
-        <f aca="false">N13*12+O13</f>
-        <v>0</v>
-      </c>
-      <c r="Z13" s="28" t="str">
-        <f aca="false">IF(I13="","",I13-U13)</f>
+      <c r="Y13" s="28" t="n">
+        <f aca="false">ROUND(V13/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="28" t="n">
+        <f aca="false">S13-R13-T13-U13-Y13</f>
+        <v>0</v>
+      </c>
+      <c r="AA13" s="17" t="n">
+        <f aca="false">P13*12+Q13</f>
+        <v>0</v>
+      </c>
+      <c r="AB13" s="28" t="str">
+        <f aca="false">IF(I13="","",I13-W13)</f>
         <v/>
       </c>
     </row>
@@ -4190,46 +4493,51 @@
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
       <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
+      <c r="I14" s="26" t="str">
+        <f aca="false">IF(OR(J14="",K14=""),"",ROUND((J14-T14-U14)*12/(K14/100),0))</f>
+        <v/>
+      </c>
+      <c r="J14" s="26"/>
+      <c r="K14" s="27"/>
       <c r="L14" s="19"/>
-      <c r="M14" s="27"/>
+      <c r="M14" s="19"/>
       <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="26"/>
-      <c r="Q14" s="26"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
       <c r="R14" s="26"/>
       <c r="S14" s="26"/>
       <c r="T14" s="26"/>
-      <c r="U14" s="28" t="n">
+      <c r="U14" s="26"/>
+      <c r="V14" s="26"/>
+      <c r="W14" s="28" t="n">
         <f aca="false">F14+G14</f>
         <v>0</v>
       </c>
-      <c r="V14" s="28" t="n">
+      <c r="X14" s="28" t="n">
         <f aca="false">G14-H14</f>
         <v>0</v>
       </c>
-      <c r="W14" s="28" t="n">
-        <f aca="false">ROUND(T14/12,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X14" s="28" t="n">
-        <f aca="false">Q14-P14-R14-S14-W14</f>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="17" t="n">
-        <f aca="false">N14*12+O14</f>
-        <v>0</v>
-      </c>
-      <c r="Z14" s="28" t="str">
-        <f aca="false">IF(I14="","",I14-U14)</f>
+      <c r="Y14" s="28" t="n">
+        <f aca="false">ROUND(V14/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="28" t="n">
+        <f aca="false">S14-R14-T14-U14-Y14</f>
+        <v>0</v>
+      </c>
+      <c r="AA14" s="17" t="n">
+        <f aca="false">P14*12+Q14</f>
+        <v>0</v>
+      </c>
+      <c r="AB14" s="28" t="str">
+        <f aca="false">IF(I14="","",I14-W14)</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -4263,54 +4571,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>32</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="29" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>34</v>
@@ -4337,10 +4645,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="29" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>34</v>
@@ -4367,10 +4675,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="29" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>34</v>
@@ -4397,10 +4705,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="29" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>34</v>
@@ -4412,7 +4720,7 @@
         <v>1200000</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G9" s="28" t="n">
         <f aca="false">E9-D9</f>
@@ -4429,10 +4737,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>36</v>
@@ -4459,10 +4767,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>36</v>
@@ -4489,10 +4797,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>36</v>
@@ -4519,10 +4827,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="29" t="s">
         <v>90</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>88</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>36</v>
@@ -4534,7 +4842,7 @@
         <v>11000</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G13" s="28" t="n">
         <f aca="false">E13-D13</f>
@@ -4551,7 +4859,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D14" s="31" t="n">
         <f aca="false">SUM(D6:D13)</f>
@@ -4562,7 +4870,7 @@
         <v>10268500</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G14" s="31" t="n">
         <f aca="false">SUM(G6:G13)</f>
@@ -4616,65 +4924,65 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>32</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K6" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>34</v>
@@ -4689,10 +4997,10 @@
         <v>10000000</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I7" s="24" t="n">
         <f aca="false">IF(A7="","",E7-D7)</f>
@@ -4863,7 +5171,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J15" s="31" t="n">
         <f aca="false">SUM(J8:J14)</f>
@@ -4876,7 +5184,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -4913,31 +5221,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>34</v>
@@ -5078,7 +5386,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D20" s="31" t="n">
         <f aca="false">SUM(D6:D19)</f>
@@ -5121,28 +5429,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>47</v>
@@ -5151,24 +5459,24 @@
         <v>48</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>3000000</v>
@@ -5330,123 +5638,123 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B5" s="28" t="n">
         <f aca="false">有価証券!H14</f>
         <v>20831200</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B6" s="28" t="n">
         <f aca="false">有価証券!H14-有価証券!I14</f>
         <v>6116000</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B7" s="28" t="n">
         <f aca="false">保険!J15</f>
         <v>0</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B8" s="28" t="n">
         <f aca="false">保険!J15-保険!K15</f>
         <v>0</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">預貯金!D20</f>
         <v>0</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B10" s="33" t="n">
         <f aca="false">有価証券!H14+保険!J15+預貯金!D20</f>
         <v>20831200</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B11" s="28" t="n">
         <f aca="false">有価証券!H14+保険!J15-有価証券!I14-保険!K15</f>
         <v>6116000</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B14" s="28" t="n">
-        <f aca="false">SUM(不動産!$U$6:$U$14)</f>
+        <f aca="false">SUM(不動産!$W$6:$W$14)</f>
         <v>0</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B15" s="28" t="n">
         <f aca="false">SUM(不動産!$F$6:$F$14)</f>
@@ -5456,19 +5764,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B16" s="28" t="n">
         <f aca="false">SUM(不動産!$G$6:$G$14)</f>
         <v>0</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B17" s="28" t="n">
         <f aca="false">SUM(不動産!$H$6:$H$14)</f>
@@ -5478,84 +5786,84 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B18" s="28" t="n">
-        <f aca="false">SUM(不動産!$V$6:$V$14)</f>
+        <f aca="false">SUM(不動産!$X$6:$X$14)</f>
         <v>0</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B19" s="34" t="n">
-        <f aca="false">IFERROR(SUM(不動産!$V$6:$V$14)/SUM(不動産!$G$6:$G$14),0)</f>
+        <f aca="false">IFERROR(SUM(不動産!$X$6:$X$14)/SUM(不動産!$G$6:$G$14),0)</f>
         <v>0</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B20" s="28" t="n">
-        <f aca="false">SUM(不動産!$X$6:$X$14)</f>
+        <f aca="false">SUM(不動産!$Z$6:$Z$14)</f>
         <v>0</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B21" s="28" t="n">
         <f aca="false">IF(COUNT(不動産!$I$6:$I$14)=0,0,SUM(不動産!$I$6:$I$14))</f>
         <v>0</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B22" s="28" t="n">
-        <f aca="false">IF(COUNT(不動産!$I$6:$I$14)=0,0,SUM(不動産!$Z$6:$Z$14))</f>
+        <f aca="false">IF(COUNT(不動産!$I$6:$I$14)=0,0,SUM(不動産!$AB$6:$AB$14))</f>
         <v>0</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="35" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B23" s="34" t="n">
         <f aca="false">IFERROR(SUM(不動産!$H$6:$H$14)/SUM(不動産!$I$6:$I$14),0)</f>
         <v>0</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B26" s="28" t="n">
         <f aca="false">SUM(不動産!$H$6:$H$14)</f>
@@ -5565,173 +5873,173 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B27" s="28" t="n">
         <f aca="false">SUM(その他の借入!E7:E15)</f>
         <v>0</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="32" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B28" s="33" t="n">
         <f aca="false">SUM(不動産!$H$6:$H$14)+SUM(その他の借入!E7:E15)</f>
         <v>0</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B31" s="36" t="str">
         <f aca="false">COUNT(不動産!$I$6:$I$14)&amp;" / "&amp;COUNTA(不動産!$A$6:$A$14)&amp;" 物件"</f>
         <v>0 / 0 物件</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B32" s="28" t="n">
         <f aca="false">IF(COUNT(不動産!$I$6:$I$14)&lt;&gt;COUNTA(不動産!$A$6:$A$14),"時価未入力あり",有価証券!H14+保険!J15+預貯金!D20+SUM(不動産!$I$6:$I$14))</f>
         <v>20831200</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="32" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B33" s="33" t="n">
         <f aca="false">IF(COUNT(不動産!$I$6:$I$14)&lt;&gt;COUNTA(不動産!$A$6:$A$14),"時価未入力あり",有価証券!H14+保険!J15+預貯金!D20+SUM(不動産!$I$6:$I$14)-(SUM(不動産!$H$6:$H$14)+SUM(その他の借入!E7:E15)))</f>
         <v>20831200</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B38" s="36" t="str">
         <f aca="false">IF(SUMPRODUCT((不動産!A6:A14&lt;&gt;"")*(不動産!H6:H14&gt;不動産!G6:G14))&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B39" s="36" t="str">
         <f aca="false">IF(SUMPRODUCT((その他の借入!A7:A15&lt;&gt;"")*(その他の借入!E7:E15&gt;その他の借入!D7:D15))&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B40" s="36" t="str">
         <f aca="false">IF(SUMPRODUCT((不動産!F6:H14&lt;0)*1)+SUMPRODUCT((有価証券!D6:E13&lt;0)*1)&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B41" s="36" t="str">
         <f aca="false">IF(SUMPRODUCT(ISERROR(MATCH(有価証券!C6:C13,基本情報!$A$10:$A$13,0))*1)&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B42" s="36" t="str">
         <f aca="false">IF(OR(基本情報!B4="",基本情報!B5=""),"要確認","OK")</f>
         <v>OK</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B43" s="36" t="str">
-        <f aca="false">IF(SUMPRODUCT((不動産!A6:A14&lt;&gt;"")*((不動産!O6:O14&lt;0)+(不動産!O6:O14&gt;11)))&gt;0,"要確認","OK")</f>
+        <f aca="false">IF(SUMPRODUCT((不動産!A6:A14&lt;&gt;"")*((不動産!Q6:Q14&lt;0)+(不動産!Q6:Q14&gt;11)))&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B44" s="36" t="str">
         <f aca="false">IF(SUMPRODUCT((不動産!A6:A14&lt;&gt;"")*(不動産!I6:I14&gt;0)*(不動産!I6:I14&lt;不動産!H6:H14))&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B45" s="36" t="str">
         <f aca="false">IF(SUMPRODUCT((保険!A8:A14&lt;&gt;"")*ISERROR(MATCH(保険!C8:C14,基本情報!$A$10:$A$13,0)))&gt;0,"要確認","OK")</f>
         <v>OK</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
